--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:45</t>
+    <t xml:space="preserve">2026-09-09 23:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:45</t>
+    <t xml:space="preserve">2026-09-18 10:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:33</t>
+    <t xml:space="preserve">2026-09-23 13:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:06</t>
+    <t xml:space="preserve">2026-10-02 15:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_p_monto_aps_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:26</t>
+    <t xml:space="preserve">2026-10-05 13:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1045,7 +1045,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>74575.62</v>
+        <v>74575.63</v>
       </c>
     </row>
     <row r="27">
